--- a/Teoría de la información/AF2/Canal Binario Simétrico/Ejercicio A - Matríz de Transiciones.xlsx
+++ b/Teoría de la información/AF2/Canal Binario Simétrico/Ejercicio A - Matríz de Transiciones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\Semestre-EneJun2026\Teoría de la información\AF2\Canal Binario Simétrico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Repositorios\Semestre-EneJun2026\Teoría de la información\AF2\Canal Binario Simétrico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0378AB94-8ED7-45A8-932E-FF25133994B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97D10C8-9E71-4980-9C8A-E4D5DCC50A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D86E2F76-B9DA-43B6-8FD3-A59139A4776F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12216" xr2:uid="{D86E2F76-B9DA-43B6-8FD3-A59139A4776F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -95,9 +84,6 @@
     <t>q = Probabilidad de recibir algo incierto de lo que se haya mandado</t>
   </si>
   <si>
-    <t>r = Probabilidad de recibir algo Directamente DISTINTo de lo que se mandó</t>
-  </si>
-  <si>
     <t>Dado que es un canal simétrico, las probabilidades se invierten para el envío de un 1:</t>
   </si>
   <si>
@@ -132,6 +118,9 @@
   </si>
   <si>
     <t>+p</t>
+  </si>
+  <si>
+    <t>r = Probabilidad de recibir algo Directamente DISTINTO de lo que se mandó</t>
   </si>
 </sst>
 </file>
@@ -208,18 +197,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -227,6 +204,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -662,20 +651,20 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" t="s">
         <v>19</v>
       </c>
-      <c r="K16" t="s">
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K17" s="9" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="K17" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>12</v>
@@ -686,8 +675,8 @@
       <c r="N17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O17" s="7" t="s">
-        <v>22</v>
+      <c r="O17" s="11" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.3">
@@ -700,7 +689,7 @@
       <c r="D18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K18" s="5"/>
+      <c r="K18" s="10"/>
       <c r="L18" s="4" t="s">
         <v>15</v>
       </c>
@@ -710,7 +699,7 @@
       <c r="N18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O18" s="8"/>
+      <c r="O18" s="12"/>
     </row>
     <row r="19" spans="2:15" ht="18" x14ac:dyDescent="0.35">
       <c r="B19" s="1">
@@ -734,10 +723,10 @@
         <v>14</v>
       </c>
       <c r="J20" t="s">
+        <v>22</v>
+      </c>
+      <c r="M20" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="18" x14ac:dyDescent="0.35">
@@ -750,31 +739,31 @@
       <c r="D21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="J21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="L21" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L21" s="10" t="s">
+      <c r="M21" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="M21" s="10" t="s">
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="J22" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K22" s="12" t="s">
+      <c r="L22" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L22" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>28</v>
+      <c r="M22" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
